--- a/LDL_HbA1c_用量別_薬価付き_日本語表_英語タイトル引用付き.xlsx
+++ b/LDL_HbA1c_用量別_薬価付き_日本語表_英語タイトル引用付き.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawagoeyasuhito/Desktop/jp_outcomes_regimen_selector/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawagoeyasuhito/Desktop/jp_outcomes_mvp_complete_final_backup_20251228_103719/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{146F2F0D-08A9-234F-90D7-9821D4F911A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881A1575-EA61-9F42-B408-C52A4E374040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="2180" windowWidth="20600" windowHeight="12760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LDL用量別（薬価付き）" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="155">
   <si>
     <t>分類</t>
   </si>
@@ -324,6 +324,169 @@
   </si>
   <si>
     <t>横浜市大入札資料</t>
+  </si>
+  <si>
+    <t>GLP-1受容体作動薬（経口）</t>
+  </si>
+  <si>
+    <t>リベルサス（セマグルチド） 3 mg/日</t>
+  </si>
+  <si>
+    <t>HbA1c −1.1%（開始用量）</t>
+  </si>
+  <si>
+    <t>悪心・下痢（5%以上）、便秘・嘔吐・腹部不快感・腹痛・消化不良（1〜5%未満）</t>
+  </si>
+  <si>
+    <t>Yabe D, et al. Safety and efficacy of oral semaglutide versus dulaglutide in Japanese patients with type 2 diabetes (PIONEER 10): an open-label, randomised, active-controlled, phase 3a trial. Lancet Diabetes Endocrinol. 2020;8(5):392-406.</t>
+  </si>
+  <si>
+    <t>143.2 円/錠</t>
+  </si>
+  <si>
+    <t>52,268 円/年</t>
+  </si>
+  <si>
+    <t>143.2 × 365 = 52,268 円/年</t>
+  </si>
+  <si>
+    <t>リベルサス（セマグルチド） 7 mg/日</t>
+  </si>
+  <si>
+    <t>HbA1c −1.7%</t>
+  </si>
+  <si>
+    <t>334.2 円/錠</t>
+  </si>
+  <si>
+    <t>121,983 円/年</t>
+  </si>
+  <si>
+    <t>334.2 × 365 = 121,983 円/年</t>
+  </si>
+  <si>
+    <t>リベルサス（セマグルチド） 14 mg/日</t>
+  </si>
+  <si>
+    <t>HbA1c −2.0%</t>
+  </si>
+  <si>
+    <t>501.3 円/錠</t>
+  </si>
+  <si>
+    <t>182,975 円/年</t>
+  </si>
+  <si>
+    <t>501.3 × 365 = 182,975 円/年</t>
+  </si>
+  <si>
+    <t>GLP-1受容体作動薬（皮下）</t>
+  </si>
+  <si>
+    <t>オゼンピック（セマグルチド） 0.5 mg/週</t>
+  </si>
+  <si>
+    <t>HbA1c −1.3%（対シタグリプチン ETD −0.77%, 95%CI −0.92〜−0.62）</t>
+  </si>
+  <si>
+    <t>悪心 18%、下痢 13%、投与中止に至る有害事象 8%</t>
+  </si>
+  <si>
+    <t>Ahrén B, et al. Efficacy and safety of once-weekly semaglutide versus once-daily sitagliptin in patients with type 2 diabetes (SUSTAIN 2): a 56-week, double-blind, phase 3a, randomised trial. Lancet Diabetes Endocrinol. 2017;5(5):341-354.</t>
+  </si>
+  <si>
+    <t>2,466 円/回</t>
+  </si>
+  <si>
+    <t>128,232 円/年</t>
+  </si>
+  <si>
+    <t>2,466 × 52 = 128,232 円/年</t>
+  </si>
+  <si>
+    <t>KEGG薬価データ（週1回換算）</t>
+  </si>
+  <si>
+    <t>オゼンピック（セマグルチド） 1.0 mg/週</t>
+  </si>
+  <si>
+    <t>HbA1c −1.6%（対シタグリプチン ETD −1.06%, 95%CI −1.21〜−0.91）</t>
+  </si>
+  <si>
+    <t>悪心 18%、下痢 13%、投与中止に至る有害事象 10%</t>
+  </si>
+  <si>
+    <t>4,932 円/回</t>
+  </si>
+  <si>
+    <t>256,464 円/年</t>
+  </si>
+  <si>
+    <t>4,932 × 52 = 256,464 円/年</t>
+  </si>
+  <si>
+    <t>GIP/GLP-1受容体作動薬</t>
+  </si>
+  <si>
+    <t>マンジャロ（チルゼパチド） 5 mg/週</t>
+  </si>
+  <si>
+    <t>HbA1c −2.37%（対デュラグルチド0.75mg 群差 −1.09%, 95%CI −1.27〜−0.90）</t>
+  </si>
+  <si>
+    <t>副作用発現頻度 33.9%、悪心 10.7%</t>
+  </si>
+  <si>
+    <t>Inagaki N, et al. Efficacy and safety of tirzepatide monotherapy compared with dulaglutide in Japanese patients with type 2 diabetes (SURPASS J-mono): a double-blind, multicentre, randomised, phase 3 trial. Lancet Diabetes Endocrinol. 2022;10(9):623-633.</t>
+  </si>
+  <si>
+    <t>3,848 円/回</t>
+  </si>
+  <si>
+    <t>200,096 円/年</t>
+  </si>
+  <si>
+    <t>3,848 × 52 = 200,096 円/年</t>
+  </si>
+  <si>
+    <t>マンジャロ（チルゼパチド） 10 mg/週</t>
+  </si>
+  <si>
+    <t>HbA1c −2.55%（対デュラグルチド0.75mg 群差 −1.27%, 95%CI −1.45〜−1.08）</t>
+  </si>
+  <si>
+    <t>副作用発現頻度 46.3%、悪心 12.4%、下痢 11.6%</t>
+  </si>
+  <si>
+    <t>7,696 円/回</t>
+  </si>
+  <si>
+    <t>400,192 円/年</t>
+  </si>
+  <si>
+    <t>7,696 × 52 = 400,192 円/年</t>
+  </si>
+  <si>
+    <t>マンジャロ（チルゼパチド） 15 mg/週</t>
+  </si>
+  <si>
+    <t>HbA1c −2.82%（対デュラグルチド0.75mg 群差 −1.53%, 95%CI −1.71〜−1.35）</t>
+  </si>
+  <si>
+    <t>副作用発現頻度 41.3%、悪心 17.4%、下痢 10.7%</t>
+  </si>
+  <si>
+    <t>11,544 円/回</t>
+  </si>
+  <si>
+    <t>600,288 円/年</t>
+  </si>
+  <si>
+    <t>11,544 × 52 = 600,288 円/年</t>
+  </si>
+  <si>
+    <t>悪心・下痢（5%以上）、便秘・嘔吐・腹部不快感・腹痛・消化不良（1〜5%未満）</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -389,10 +552,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -700,6 +866,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
@@ -999,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1147,8 +1316,241 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:9" ht="409.6">
+      <c r="A6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="409.6">
+      <c r="A7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="409.6">
+      <c r="A8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="409.6">
+      <c r="A9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="409.6">
+      <c r="A10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="409.6">
+      <c r="A11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="409.6">
+      <c r="A12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="409.6">
+      <c r="A13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>